--- a/VerveStacks_CHE_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_CHE_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9F56DF19-1DF7-4395-9E93-738CBB378288}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A228A3B4-AA02-4944-AE7D-CC4AD33A2BB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHE_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_CHE_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A228A3B4-AA02-4944-AE7D-CC4AD33A2BB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9BA5BFB7-5C8F-49B4-8E9E-D9F2401B0FBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHE_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_CHE_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9BA5BFB7-5C8F-49B4-8E9E-D9F2401B0FBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{113B6615-39BD-4B74-AC5D-62C9C2B23665}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHE_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_CHE_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{113B6615-39BD-4B74-AC5D-62C9C2B23665}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FDC62837-BA17-4776-A97D-04BE4C4FD07A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_CHE_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_CHE_grids/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CHE_grids\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FDC62837-BA17-4776-A97D-04BE4C4FD07A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{77789040-C32F-4090-863B-E4204FBE5B74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
